--- a/duoki_editor/resources/data/blank/服装店-印图案-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-印图案-1-blank.xlsx
@@ -148,7 +148,7 @@
     <t>找不到的话，要不要打开魔镜试试？快告诉我吧</t>
   </si>
   <si>
-    <t>{user_name}快看这里！我们用魔镜找到他吧。</t>
+    <t>{user_name}快看这里！我们用魔镜找到它吧。</t>
   </si>
   <si>
     <t>为了找到{word_cn}，需要大声念出咒语，"{word_en}"！</t>
